--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486838_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486838_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2645</v>
+        <v>4.5608</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6106</v>
+        <v>1.9069</v>
       </c>
       <c r="F2" t="n">
         <v>2.6539</v>
@@ -610,10 +610,10 @@
         <v>0.9654</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3584</v>
+        <v>0.9379</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.214</v>
+        <v>0.0822</v>
       </c>
       <c r="U2" t="n">
         <v>0.8556</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0288</v>
+        <v>2.6596</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5729</v>
+        <v>0.6249</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4559</v>
+        <v>2.0348</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2069</v>
+        <v>0.4623</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3033</v>
+        <v>1.0411</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.0964</v>
+        <v>-0.5787</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.351</v>
+        <v>1.4013</v>
       </c>
       <c r="K3" t="n">
-        <v>1.028</v>
+        <v>1.3177</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.379</v>
+        <v>0.0837</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5579</v>
+        <v>-0.9389999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2753</v>
+        <v>-0.2766</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2826</v>
+        <v>-0.6624</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9654</v>
+        <v>-2.1239</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7723</v>
+        <v>2.1239</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1308</v>
+        <v>0.0275</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6616</v>
+        <v>-0.1659</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4692</v>
+        <v>0.1934</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8842</v>
+        <v>2.1698</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2277</v>
+        <v>1.5133</v>
       </c>
       <c r="X3" t="n">
         <v>0.6565</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7934</v>
+        <v>2.622</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.1662</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7272</v>
+        <v>2.4559</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.624</v>
+        <v>0.2069</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1313</v>
+        <v>1.3033</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4928</v>
+        <v>-1.0964</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7055</v>
+        <v>-0.351</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0613</v>
+        <v>1.028</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6442</v>
+        <v>-1.379</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0815</v>
+        <v>0.5579</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.2753</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1514</v>
+        <v>0.2826</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5446</v>
+        <v>0.7241</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9648</v>
+        <v>0.2548</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5798</v>
+        <v>0.4692</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2856</v>
+        <v>1.8842</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.72</v>
+        <v>2.2663</v>
       </c>
       <c r="E5" t="n">
         <v>-0.022</v>
       </c>
       <c r="F5" t="n">
-        <v>1.742</v>
+        <v>2.2883</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9772</v>
@@ -844,13 +844,13 @@
         <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4912</v>
+        <v>0.0551</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0558</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4354</v>
+        <v>0.1109</v>
       </c>
       <c r="V5" t="n">
         <v>4.5399</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4791</v>
+        <v>1.1591</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2577</v>
+        <v>-0.444</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7368</v>
+        <v>1.603</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4623</v>
+        <v>-0.624</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0411</v>
+        <v>-0.1313</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5787</v>
+        <v>-0.4928</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4013</v>
+        <v>-0.7055</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3177</v>
+        <v>-0.0613</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0837</v>
+        <v>-0.6442</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9389999999999999</v>
+        <v>0.0815</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2766</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6624</v>
+        <v>0.1514</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.1585</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1239</v>
+        <v>-0.1931</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1239</v>
+        <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.153</v>
+        <v>0.9102</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0485</v>
+        <v>0.4546</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1045</v>
+        <v>0.4556</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1698</v>
+        <v>-0.2856</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6565</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4337</v>
+        <v>0.3028</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4548</v>
+        <v>0.1997</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.021</v>
+        <v>0.1031</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0351</v>
@@ -1000,13 +1000,13 @@
         <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2757</v>
+        <v>0.1448</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4136</v>
+        <v>0.1585</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1378</v>
+        <v>-0.0137</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>I. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1454</v>
+        <v>-0.6735</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0394</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.894</v>
+        <v>-0.0419</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8546</v>
+        <v>-1.2045</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.8756</v>
+        <v>-0.7863</v>
       </c>
       <c r="I8" t="n">
-        <v>2.021</v>
+        <v>-0.4182</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.253</v>
+        <v>-0.1832</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.84</v>
+        <v>-0.0273</v>
       </c>
       <c r="L8" t="n">
-        <v>1.587</v>
+        <v>-0.1559</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6016</v>
+        <v>-1.0212</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0355</v>
+        <v>-0.759</v>
       </c>
       <c r="O8" t="n">
-        <v>0.434</v>
+        <v>-0.2623</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5446</v>
+        <v>0.5792</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0892</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5446</v>
+        <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>3.895</v>
+        <v>-0.0483</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4887</v>
+        <v>-0.4484</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4063</v>
+        <v>0.4001</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6412</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8142</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. MONTERO ISLA</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6031</v>
+        <v>-1.4606</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7351</v>
+        <v>-2.5914</v>
       </c>
       <c r="F9" t="n">
-        <v>0.132</v>
+        <v>1.1308</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2045</v>
+        <v>-1.3472</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7863</v>
+        <v>-0.6283</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4182</v>
+        <v>-0.7188</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1832</v>
+        <v>-0.8835</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0273</v>
+        <v>0.4072</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1559</v>
+        <v>-1.2907</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0212</v>
+        <v>-0.4637</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.759</v>
+        <v>-1.0355</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2623</v>
+        <v>0.5719</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5792</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5792</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0221</v>
+        <v>0.5584</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5518</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.574</v>
+        <v>0.6211</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>H. APARICIO RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1406</v>
+        <v>-2.2912</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.75</v>
+        <v>-1.6768</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6094000000000001</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3472</v>
+        <v>-1.9601</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6283</v>
+        <v>-0.5314</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7188</v>
+        <v>-1.4287</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8835</v>
+        <v>-1.5525</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4072</v>
+        <v>-0.2549</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2907</v>
+        <v>-1.2976</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4637</v>
+        <v>-0.4075</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0355</v>
+        <v>-0.2764</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5719</v>
+        <v>-0.1311</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5446</v>
+        <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1217</v>
+        <v>0.1242</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2213</v>
+        <v>-0.1242</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.2485</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5712</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRÍGUEZ</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6084</v>
+        <v>-2.3715</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.994</v>
+        <v>-2.0736</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.298</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9601</v>
+        <v>-0.8546</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5314</v>
+        <v>-2.8756</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4287</v>
+        <v>2.021</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5525</v>
+        <v>-0.253</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2549</v>
+        <v>-1.84</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2976</v>
+        <v>1.587</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4075</v>
+        <v>-0.6016</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2764</v>
+        <v>-1.0355</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1311</v>
+        <v>0.434</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7723</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.0892</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7723</v>
+        <v>1.5446</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.193</v>
+        <v>1.6689</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4415</v>
+        <v>0.4545</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2485</v>
+        <v>1.2144</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2277</v>
+        <v>-1.6412</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.8142</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2277</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.222000000000001</v>
+        <v>6.7738</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0937</v>
+        <v>-4.541700000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>11.3158</v>
+        <v>11.3155</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5521</v>
@@ -1360,16 +1360,16 @@
         <v>-3.4513</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8993</v>
+        <v>1.899299999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04549999999999965</v>
+        <v>0.04549999999999998</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3499999999999999</v>
+        <v>0.3500000000000003</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3045000000000002</v>
+        <v>-0.3045</v>
       </c>
       <c r="M12" t="n">
         <v>-1.5973</v>
@@ -1390,19 +1390,19 @@
         <v>11.5846</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5509</v>
+        <v>5.1028</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.004200000000000037</v>
+        <v>0.5476</v>
       </c>
       <c r="U12" t="n">
-        <v>4.555299999999999</v>
+        <v>4.555099999999999</v>
       </c>
       <c r="V12" t="n">
         <v>5.1538</v>
       </c>
       <c r="W12" t="n">
-        <v>8.380700000000001</v>
+        <v>8.380699999999999</v>
       </c>
       <c r="X12" t="n">
         <v>-3.2269</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. GARCIA NAVARO</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6719</v>
+        <v>2.1712</v>
       </c>
       <c r="E13" t="n">
-        <v>2.016</v>
+        <v>0.3308</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3441</v>
+        <v>1.8404</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1735</v>
+        <v>2.2402</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4968</v>
+        <v>2.455</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3232</v>
+        <v>-0.2148</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6961000000000001</v>
+        <v>1.3931</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1242</v>
+        <v>2.7314</v>
       </c>
       <c r="L13" t="n">
-        <v>0.572</v>
+        <v>-1.3383</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8697</v>
+        <v>0.847</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6209</v>
+        <v>-0.2764</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2487</v>
+        <v>1.1235</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1546</v>
+        <v>-1.0343</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1934</v>
+        <v>-1.0623</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0388</v>
+        <v>0.028</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>D. GARCIA NAVARO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.567</v>
+        <v>1.6678</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1239</v>
+        <v>1.9126</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4431</v>
+        <v>-0.2448</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2402</v>
+        <v>-0.1735</v>
       </c>
       <c r="H14" t="n">
-        <v>2.455</v>
+        <v>-0.4968</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2148</v>
+        <v>0.3232</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3931</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7314</v>
+        <v>0.1242</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3383</v>
+        <v>0.572</v>
       </c>
       <c r="M14" t="n">
-        <v>0.847</v>
+        <v>-0.8697</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2764</v>
+        <v>-0.6209</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1235</v>
+        <v>-0.2487</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6385</v>
+        <v>-0.1587</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2692</v>
+        <v>-0.2969</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3693</v>
+        <v>0.1381</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. ALONSO MENOR</t>
+          <t>D. GUIJARRO GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1007</v>
+        <v>1.1481</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0887</v>
+        <v>0.5382</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0121</v>
+        <v>0.6099</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7641</v>
+        <v>0.5162</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>1.4974</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7641</v>
+        <v>-0.9812</v>
       </c>
       <c r="J15" t="n">
-        <v>0.337</v>
+        <v>1.5794</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2756</v>
+        <v>2.1875</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6127</v>
+        <v>-0.6081</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4271</v>
+        <v>-1.0632</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2756</v>
+        <v>-0.6901</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1514</v>
+        <v>-0.3731</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5792</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5792</v>
+        <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2426</v>
+        <v>-0.3794</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2484</v>
+        <v>-0.6004</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0058</v>
+        <v>0.221</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.1698</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ESTEBANEZ ESCUDERO</t>
+          <t>L. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5629999999999999</v>
+        <v>1.1296</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2082</v>
+        <v>0.1921</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7712</v>
+        <v>0.9376</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9977</v>
+        <v>0.7641</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4687</v>
+        <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.529</v>
+        <v>0.7641</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7575</v>
+        <v>0.337</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2624</v>
+        <v>-0.2756</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4952</v>
+        <v>0.6127</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2401</v>
+        <v>0.4271</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2063</v>
+        <v>0.2756</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0338</v>
+        <v>0.1514</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6011</v>
+        <v>-0.2137</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9657</v>
+        <v>-0.145</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3646</v>
+        <v>-0.0687</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1851</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. GUIJARRO GONZALEZ</t>
+          <t>M. ESTEBANEZ ESCUDERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2752</v>
+        <v>0.7988</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1857</v>
+        <v>0.1021</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4609</v>
+        <v>0.6967</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5162</v>
+        <v>0.9977</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4974</v>
+        <v>0.4687</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9812</v>
+        <v>0.529</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5794</v>
+        <v>0.7575</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1875</v>
+        <v>0.2624</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6081</v>
+        <v>0.4952</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0632</v>
+        <v>0.2401</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6901</v>
+        <v>0.2063</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3731</v>
+        <v>0.0338</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7377</v>
+        <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2523</v>
+        <v>-0.3654</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3244</v>
+        <v>-0.6555</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.2901</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1698</v>
+        <v>-1.1851</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2856</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0201</v>
+        <v>0.2779</v>
       </c>
       <c r="E18" t="n">
         <v>-2.9402</v>
       </c>
       <c r="F18" t="n">
-        <v>2.92</v>
+        <v>3.218</v>
       </c>
       <c r="G18" t="n">
         <v>1.2254</v>
@@ -1858,13 +1858,13 @@
         <v>2.1239</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.153</v>
+        <v>-0.855</v>
       </c>
       <c r="T18" t="n">
         <v>-0.4418</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.4132</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2856</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.404</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1536</v>
+        <v>-0.2601</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5576</v>
+        <v>-0.6072</v>
       </c>
       <c r="G19" t="n">
         <v>0.9839</v>
@@ -1936,13 +1936,13 @@
         <v>2.1239</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4193</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3042</v>
+        <v>-0.7178</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1151</v>
+        <v>-0.1648</v>
       </c>
       <c r="V19" t="n">
         <v>-2.1271</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0137</v>
+        <v>-0.9889</v>
       </c>
       <c r="E20" t="n">
         <v>-0.7447</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2691</v>
+        <v>-0.2442</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6895</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0386</v>
+        <v>-0.0138</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2856</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9813</v>
+        <v>-2.3868</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.538</v>
+        <v>-2.7448</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5567</v>
+        <v>0.3581</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4282</v>
@@ -2092,13 +2092,13 @@
         <v>1.1585</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4469</v>
+        <v>0.0414</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3859</v>
+        <v>0.1791</v>
       </c>
       <c r="U21" t="n">
-        <v>0.061</v>
+        <v>-0.1377</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.371</v>
+        <v>-3.7072</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9552</v>
+        <v>-2.0928</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4158</v>
+        <v>-1.6144</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3926</v>
@@ -2170,13 +2170,13 @@
         <v>1.1585</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3845</v>
+        <v>0.0482</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5166</v>
+        <v>0.379</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1321</v>
+        <v>-0.3307</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5559</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6097</v>
+        <v>-5.4651</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.1257</v>
+        <v>-5.6086</v>
       </c>
       <c r="F23" t="n">
-        <v>0.516</v>
+        <v>0.1435</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4916</v>
@@ -2248,13 +2248,13 @@
         <v>1.5446</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8824</v>
+        <v>-0.7377</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.6555</v>
+        <v>-1.1384</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7731</v>
+        <v>0.4006</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8842</v>
@@ -2284,10 +2284,10 @@
         <v>-6.222</v>
       </c>
       <c r="E24" t="n">
-        <v>-11.3155</v>
+        <v>-11.3154</v>
       </c>
       <c r="F24" t="n">
-        <v>5.0934</v>
+        <v>5.093600000000001</v>
       </c>
       <c r="G24" t="n">
         <v>1.552099999999999</v>
@@ -2299,7 +2299,7 @@
         <v>-1.8994</v>
       </c>
       <c r="J24" t="n">
-        <v>1.5973</v>
+        <v>1.597299999999999</v>
       </c>
       <c r="K24" t="n">
         <v>3.8013</v>
@@ -2311,10 +2311,10 @@
         <v>-0.0454</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3498</v>
+        <v>-0.3497999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3043999999999997</v>
+        <v>0.3043999999999998</v>
       </c>
       <c r="P24" t="n">
         <v>1.9308</v>
@@ -2326,16 +2326,16 @@
         <v>13.5155</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.550999999999999</v>
+        <v>-4.551</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.555300000000001</v>
+        <v>-4.5552</v>
       </c>
       <c r="U24" t="n">
-        <v>0.004199999999999759</v>
+        <v>0.004100000000000048</v>
       </c>
       <c r="V24" t="n">
-        <v>-5.153700000000001</v>
+        <v>-5.1537</v>
       </c>
       <c r="W24" t="n">
         <v>3.226900000000001</v>
